--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:35</t>
+    <t xml:space="preserve">2026-09-09 23:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:33</t>
+    <t xml:space="preserve">2026-09-17 14:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:28</t>
+    <t xml:space="preserve">2026-09-23 12:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_aysen.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:55</t>
+    <t xml:space="preserve">2026-10-01 23:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre salario mínimo (%)</t>
+    <t xml:space="preserve">% con ingreso igual al mínimo</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -103,9 +103,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre salario mínimo</t>
   </si>
 </sst>
 </file>
@@ -741,7 +738,7 @@
         <v>28</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:23</t>
+    <t xml:space="preserve">2026-10-02 11:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:28</t>
+    <t xml:space="preserve">2026-10-02 15:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:19</t>
+    <t xml:space="preserve">2026-10-04 09:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:36</t>
+    <t xml:space="preserve">2026-10-05 12:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
